--- a/NuevasNotas/Vespertina/Resultados_Auditoria_Notas/Matriz_Marcada_4AV.xlsx
+++ b/NuevasNotas/Vespertina/Resultados_Auditoria_Notas/Matriz_Marcada_4AV.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -58,10 +58,16 @@
       <sz val="12"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -91,24 +97,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="003B82F6"/>
+        <bgColor rgb="003B82F6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00E5E7EB"/>
         <bgColor rgb="00E5E7EB"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F3F4F6"/>
-        <bgColor rgb="00F3F4F6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -207,11 +207,16 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -258,18 +263,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -653,13 +655,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -671,142 +674,69 @@
       <c r="B1" s="18" t="n"/>
       <c r="C1" s="18" t="n"/>
       <c r="D1" s="18" t="n"/>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="19" t="inlineStr">
-        <is>
-          <t>Curso</t>
-        </is>
-      </c>
-      <c r="B2" s="19" t="inlineStr">
+      <c r="E1" s="18" t="n"/>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="19" t="inlineStr">
+        <is>
+          <t>▶ CURSO: 4AV</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="20" t="inlineStr">
         <is>
           <t>Estudiante</t>
         </is>
       </c>
-      <c r="C2" s="19" t="inlineStr">
+      <c r="B4" s="20" t="inlineStr">
         <is>
           <t>Tipo de Problema</t>
         </is>
       </c>
-      <c r="D2" s="19" t="inlineStr">
-        <is>
-          <t>Detalle de la Discrepancia</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="20" t="inlineStr">
-        <is>
-          <t>4AV</t>
-        </is>
-      </c>
-      <c r="B3" s="21" t="inlineStr">
-        <is>
-          <t>ANDRADE MEJIA ALLISON DANIELA</t>
-        </is>
-      </c>
-      <c r="C3" s="20" t="inlineStr">
-        <is>
-          <t>⚠️ FALTA EN DOCENTE</t>
-        </is>
-      </c>
-      <c r="D3" s="21" t="inlineStr">
-        <is>
-          <t>El estudiante está en el reporte oficial pero falta en la matriz del docente.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="25" customHeight="1">
-      <c r="A4" s="22" t="inlineStr">
-        <is>
-          <t>4AV</t>
-        </is>
-      </c>
-      <c r="B4" s="23" t="inlineStr">
-        <is>
-          <t>ANDRADE MEJIA ALLISSON DANIELA</t>
-        </is>
-      </c>
-      <c r="C4" s="22" t="inlineStr">
-        <is>
-          <t>⚠️ FALTA EN SISTEMA</t>
-        </is>
-      </c>
-      <c r="D4" s="23" t="inlineStr">
-        <is>
-          <t>El estudiante está en la matriz del docente pero no en el reporte oficial.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="20" t="inlineStr">
-        <is>
-          <t>4AV</t>
+      <c r="C4" s="20" t="inlineStr">
+        <is>
+          <t>Materia</t>
+        </is>
+      </c>
+      <c r="D4" s="20" t="inlineStr">
+        <is>
+          <t>Docente</t>
+        </is>
+      </c>
+      <c r="E4" s="20" t="inlineStr">
+        <is>
+          <t>Sistema</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="21" t="inlineStr">
+        <is>
+          <t>TENESACA JUELA ALEXIS SEBASTIAN</t>
         </is>
       </c>
       <c r="B5" s="21" t="inlineStr">
         <is>
-          <t>BELDUMA BELDUMA KENDRA YARELI</t>
-        </is>
-      </c>
-      <c r="C5" s="20" t="inlineStr">
-        <is>
-          <t>⚠️ FALTA EN SISTEMA</t>
-        </is>
-      </c>
-      <c r="D5" s="21" t="inlineStr">
-        <is>
-          <t>El estudiante está en la matriz del docente pero no en el reporte oficial.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="25" customHeight="1">
-      <c r="A6" s="22" t="inlineStr">
-        <is>
-          <t>4AV</t>
-        </is>
-      </c>
-      <c r="B6" s="23" t="inlineStr">
-        <is>
-          <t>BELDUMA BELDUMA KENDRA YARELY</t>
-        </is>
-      </c>
-      <c r="C6" s="22" t="inlineStr">
-        <is>
-          <t>⚠️ FALTA EN DOCENTE</t>
-        </is>
-      </c>
-      <c r="D6" s="23" t="inlineStr">
-        <is>
-          <t>El estudiante está en el reporte oficial pero falta en la matriz del docente.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="25" customHeight="1">
-      <c r="A7" s="20" t="inlineStr">
-        <is>
-          <t>4AV</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t>TENESACA JUELA ALEXIS SEBASTIAN</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr">
-        <is>
           <t>❌ ERROR DE NOTA</t>
         </is>
       </c>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>Ciencias Naturales (Docente: 9.3 vs Sistema: 9.2)</t>
-        </is>
+      <c r="C5" s="22" t="inlineStr">
+        <is>
+          <t>Ciencias Naturales</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="E5" s="21" t="n">
+        <v>9.199999999999999</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A3:E3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
